--- a/outputs/excel/Part_I_template_filled.xlsx
+++ b/outputs/excel/Part_I_template_filled.xlsx
@@ -746,7 +746,7 @@
         <v>0.08156343209871987</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.07875194729931106</v>
+        <v>0.07875194570997557</v>
       </c>
       <c r="E3" s="22" t="n">
         <v>41640</v>
@@ -755,7 +755,7 @@
         <v>-0.07026498004277006</v>
       </c>
       <c r="G3" s="24" t="n">
-        <v>-0.03649865395696385</v>
+        <v>-0.03649865416421228</v>
       </c>
     </row>
     <row r="4">
@@ -768,7 +768,7 @@
         <v>0.1567724004422423</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1080748036868332</v>
+        <v>0.1080748035952949</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>41671</v>
@@ -777,7 +777,7 @@
         <v>0.02077622686678488</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.01965962031856085</v>
+        <v>0.01965962026518523</v>
       </c>
     </row>
     <row r="5">
@@ -790,7 +790,7 @@
         <v>0.0715556652917404</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.0755197646171597</v>
+        <v>0.07551976292734075</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>41699</v>
@@ -799,7 +799,7 @@
         <v>0.04467723574102896</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.01553912799890607</v>
+        <v>0.0155391281256913</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
         <v>0.520266525668013</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.7286799939744464</v>
+        <v>0.7286799798857474</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>41730</v>
@@ -821,7 +821,7 @@
         <v>0.006795170125112241</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.02734641304080924</v>
+        <v>0.02734641306038766</v>
       </c>
     </row>
     <row r="7">
@@ -834,7 +834,7 @@
         <v>-0.1676063446518038</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.07469915412113819</v>
+        <v>-0.07469915291397239</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>41760</v>
@@ -843,7 +843,7 @@
         <v>0.04339620179990861</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.006262336560474385</v>
+        <v>0.006262336674770144</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         <v>0.1344288672572242</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.13672730681815</v>
+        <v>0.1367273068063817</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>41791</v>
@@ -865,7 +865,7 @@
         <v>0.03569530268075231</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.01320043866512655</v>
+        <v>0.01320043855385788</v>
       </c>
     </row>
     <row r="9">
@@ -891,7 +891,7 @@
         <v>-0.007361026260429289</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.00634089418775552</v>
+        <v>0.00634089399497464</v>
       </c>
     </row>
     <row r="10">
@@ -902,7 +902,7 @@
         <v>0.02463494349528241</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.0387712121249143</v>
+        <v>0.03877121196595493</v>
       </c>
     </row>
     <row r="11">
@@ -913,7 +913,7 @@
         <v>-0.07531135274733532</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.03050354375449974</v>
+        <v>-0.03050354350157332</v>
       </c>
     </row>
     <row r="12">
@@ -925,7 +925,7 @@
         <v>0.00775658866595595</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.02281906801371494</v>
+        <v>0.02281906843041514</v>
       </c>
     </row>
     <row r="13">
@@ -936,7 +936,7 @@
         <v>-0.02126323916811964</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.01887228532562114</v>
+        <v>-0.01887228565706454</v>
       </c>
     </row>
     <row r="14">
@@ -947,7 +947,7 @@
         <v>-0.06901007205913473</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.03116883437874123</v>
+        <v>-0.03116883433505653</v>
       </c>
     </row>
     <row r="15">
@@ -958,7 +958,7 @@
         <v>0.007339331453900047</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0137115262182554</v>
+        <v>0.01371152603973757</v>
       </c>
     </row>
     <row r="16">
@@ -969,7 +969,7 @@
         <v>0.04141390361404322</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.03508508431879268</v>
+        <v>0.03508508435636881</v>
       </c>
     </row>
     <row r="17">
@@ -980,7 +980,7 @@
         <v>-0.03181535717049088</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.0007744917301810142</v>
+        <v>-0.0007744917573539734</v>
       </c>
     </row>
     <row r="18">
@@ -991,7 +991,7 @@
         <v>0.05520842262682887</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.02706826663122262</v>
+        <v>0.0270682666372253</v>
       </c>
     </row>
     <row r="19">
@@ -1002,7 +1002,7 @@
         <v>-0.04519396145635353</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.04631065917551878</v>
+        <v>-0.04631065920667646</v>
       </c>
     </row>
     <row r="20">
@@ -1013,7 +1013,7 @@
         <v>-0.01671837114782021</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.02770413006778343</v>
+        <v>-0.0277041300910287</v>
       </c>
     </row>
     <row r="21">
@@ -1024,7 +1024,7 @@
         <v>-0.05212452092794789</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.01860379034188642</v>
+        <v>0.01860379034121998</v>
       </c>
     </row>
     <row r="22">
@@ -1035,7 +1035,7 @@
         <v>-0.08464422338745563</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.07187086909009724</v>
+        <v>-0.07187086903754682</v>
       </c>
     </row>
     <row r="23">
@@ -1046,7 +1046,7 @@
         <v>-0.02493133275277176</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.01833165775342299</v>
+        <v>-0.01833165785473283</v>
       </c>
     </row>
     <row r="24">
@@ -1057,7 +1057,7 @@
         <v>0.06491029329859194</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.03511363678730488</v>
+        <v>0.03511363660085631</v>
       </c>
     </row>
     <row r="25">
@@ -1068,7 +1068,7 @@
         <v>-0.0357558144902735</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.02591029444436185</v>
+        <v>-0.02591029444208056</v>
       </c>
     </row>
     <row r="26">
@@ -1079,7 +1079,7 @@
         <v>-0.02106535603086771</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.01596111877501052</v>
+        <v>-0.01596111878380158</v>
       </c>
     </row>
     <row r="27">
@@ -1090,7 +1090,7 @@
         <v>-0.04230023559388479</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.04473407084893805</v>
+        <v>0.04473406834969725</v>
       </c>
     </row>
     <row r="28">
@@ -1101,7 +1101,7 @@
         <v>-0.0078763026838919</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.00243889489822054</v>
+        <v>-0.0024388990608279</v>
       </c>
     </row>
     <row r="29">
@@ -1112,7 +1112,7 @@
         <v>0.1344288672572242</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.08147079559328299</v>
+        <v>0.08147079497264535</v>
       </c>
     </row>
     <row r="30">
@@ -1123,7 +1123,7 @@
         <v>0.019650899382275</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-0.0201409321380176</v>
+        <v>-0.02014093371819024</v>
       </c>
     </row>
     <row r="31">
@@ -1134,7 +1134,7 @@
         <v>-0.03779392015602362</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.009053826483847069</v>
+        <v>0.009053828166525842</v>
       </c>
     </row>
     <row r="32">
@@ -1145,7 +1145,7 @@
         <v>0.04977529648158455</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.05887672949777369</v>
+        <v>0.05887672707655323</v>
       </c>
     </row>
     <row r="33">
@@ -1156,7 +1156,7 @@
         <v>0.04574271959133058</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.01973486261259125</v>
+        <v>0.01973485816907689</v>
       </c>
     </row>
     <row r="34">
@@ -1167,7 +1167,7 @@
         <v>0.02043609851042295</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.01247481766669782</v>
+        <v>-0.01247481344690763</v>
       </c>
     </row>
     <row r="35">
@@ -1178,7 +1178,7 @@
         <v>0.007018885117639503</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-0.005238919229533591</v>
+        <v>-0.005238919074118562</v>
       </c>
     </row>
     <row r="36">
@@ -1189,7 +1189,7 @@
         <v>0.008182529362591296</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-0.04004794132650656</v>
+        <v>-0.0400479406719685</v>
       </c>
     </row>
     <row r="37">
@@ -1200,7 +1200,7 @@
         <v>-0.03732341822162155</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-0.07469915412113819</v>
+        <v>-0.07469915291397239</v>
       </c>
     </row>
     <row r="38">
@@ -1211,7 +1211,7 @@
         <v>0.02032329511426291</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-0.02434305354521402</v>
+        <v>-0.02434305449003699</v>
       </c>
     </row>
     <row r="39">
@@ -1222,7 +1222,7 @@
         <v>0.04727385709321499</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.01357608535985715</v>
+        <v>0.01357608550579243</v>
       </c>
     </row>
     <row r="40">
@@ -1233,7 +1233,7 @@
         <v>0.02665901511045048</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.04708600857154882</v>
+        <v>0.04708600796748979</v>
       </c>
     </row>
     <row r="41">
@@ -1244,7 +1244,7 @@
         <v>0.02028145574585162</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.0201892740589598</v>
+        <v>0.02018927446922038</v>
       </c>
     </row>
     <row r="42">
@@ -1255,7 +1255,7 @@
         <v>0.01158976941153002</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.0003715570334755685</v>
+        <v>0.0003715564497607129</v>
       </c>
     </row>
     <row r="43">
@@ -1266,7 +1266,7 @@
         <v>0.01504055287089303</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.05543237695496969</v>
+        <v>0.0554323768789813</v>
       </c>
     </row>
     <row r="44">
@@ -1277,7 +1277,7 @@
         <v>0.001160368965973042</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.000901319387124734</v>
+        <v>0.0009013197658726451</v>
       </c>
     </row>
     <row r="45">
@@ -1288,7 +1288,7 @@
         <v>0.04799108027004863</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.01066299590610429</v>
+        <v>0.01066299611965773</v>
       </c>
     </row>
     <row r="46">
@@ -1299,7 +1299,7 @@
         <v>0.02768204362181925</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-0.004607831285661605</v>
+        <v>-0.004607831124146113</v>
       </c>
     </row>
     <row r="47">
@@ -1310,7 +1310,7 @@
         <v>-0.00570725226602121</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.007875082516075846</v>
+        <v>0.007875082940049287</v>
       </c>
     </row>
     <row r="48">
@@ -1321,7 +1321,7 @@
         <v>0.03870562748930086</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.007307510293602354</v>
+        <v>0.007307510240592709</v>
       </c>
     </row>
     <row r="49">
@@ -1332,7 +1332,7 @@
         <v>-0.005876212524494721</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.01364089392327828</v>
+        <v>0.01364089450924604</v>
       </c>
     </row>
     <row r="50">
@@ -1343,7 +1343,7 @@
         <v>0.05104246015880655</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.0462815568710923</v>
+        <v>0.04628155692471259</v>
       </c>
     </row>
     <row r="51">
@@ -1354,7 +1354,7 @@
         <v>0.0893234684450967</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.03724321209674699</v>
+        <v>0.0372432126422939</v>
       </c>
     </row>
     <row r="52">
@@ -1365,7 +1365,7 @@
         <v>-0.04479130657071866</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-0.02618760614260785</v>
+        <v>-0.02618760419048109</v>
       </c>
     </row>
     <row r="53">
@@ -1376,7 +1376,7 @@
         <v>-0.01880510215300218</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.01900678232749568</v>
+        <v>0.01900678106808058</v>
       </c>
     </row>
     <row r="54">
@@ -1387,7 +1387,7 @@
         <v>-0.0006726306147162645</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-0.00282253112223207</v>
+        <v>-0.002822531344317912</v>
       </c>
     </row>
     <row r="55">
@@ -1398,7 +1398,7 @@
         <v>-0.04379614011242528</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-0.05550433384790956</v>
+        <v>-0.05550433232821735</v>
       </c>
     </row>
     <row r="56">
@@ -1409,7 +1409,7 @@
         <v>-0.03727713089984806</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-0.034419906806723</v>
+        <v>-0.03441991477683013</v>
       </c>
     </row>
     <row r="57">
@@ -1420,7 +1420,7 @@
         <v>0.03580369355824013</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.01491953128754385</v>
+        <v>0.01491953329812574</v>
       </c>
     </row>
     <row r="58">
@@ -1431,7 +1431,7 @@
         <v>-0.01683805800516765</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.009778613903010396</v>
+        <v>-0.009778611968786882</v>
       </c>
     </row>
     <row r="59">
@@ -1442,7 +1442,7 @@
         <v>0.01082714347627491</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.009075954559004387</v>
+        <v>0.009075954163016309</v>
       </c>
     </row>
     <row r="60">
@@ -1453,7 +1453,7 @@
         <v>-0.08162448270734325</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.05253338333573024</v>
+        <v>-0.05253338545020794</v>
       </c>
     </row>
     <row r="61">
@@ -1464,7 +1464,7 @@
         <v>0.03803461615174045</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.02153674033240482</v>
+        <v>0.02153674073488552</v>
       </c>
     </row>
     <row r="62">
@@ -1475,7 +1475,7 @@
         <v>-0.01726815205799227</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.01953265045944296</v>
+        <v>0.01953264768293812</v>
       </c>
     </row>
     <row r="63">
@@ -1486,7 +1486,7 @@
         <v>0.07603690863090601</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.03661054394851312</v>
+        <v>0.03661054386609895</v>
       </c>
     </row>
     <row r="64">
@@ -1497,7 +1497,7 @@
         <v>-0.001483284179754729</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.0224028642232468</v>
+        <v>0.02240286231202886</v>
       </c>
     </row>
     <row r="65">
@@ -1508,7 +1508,7 @@
         <v>0.01296987343877379</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.008917643194512815</v>
+        <v>0.008917643301495151</v>
       </c>
     </row>
     <row r="66">
@@ -1519,7 +1519,7 @@
         <v>0.02224224988959288</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.008073205005376517</v>
+        <v>0.008073205459912745</v>
       </c>
     </row>
     <row r="67">
@@ -1530,7 +1530,7 @@
         <v>-0.04731589556520111</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-0.01124132433488315</v>
+        <v>-0.01124132435997483</v>
       </c>
     </row>
     <row r="68">
@@ -1541,7 +1541,7 @@
         <v>0.05641209010605747</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0437354964628522</v>
+        <v>0.0437354968493094</v>
       </c>
     </row>
     <row r="69">
@@ -1552,7 +1552,7 @@
         <v>-0.01440008118544814</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-0.005286451188886107</v>
+        <v>-0.005286450978308898</v>
       </c>
     </row>
     <row r="70">
@@ -1563,7 +1563,7 @@
         <v>-0.05710121097500874</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.01914790200737383</v>
+        <v>0.01914790261286416</v>
       </c>
     </row>
     <row r="71">
@@ -1574,7 +1574,7 @@
         <v>0.03038971883415154</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.02627845134126465</v>
+        <v>0.02627845191585233</v>
       </c>
     </row>
     <row r="72">
@@ -1585,7 +1585,7 @@
         <v>0.03558394552960962</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.02962166397401734</v>
+        <v>0.02962166351179261</v>
       </c>
     </row>
     <row r="73">
@@ -1596,7 +1596,7 @@
         <v>-0.01065678404993961</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-0.03493622520940308</v>
+        <v>-0.03493622720370018</v>
       </c>
     </row>
     <row r="74">
@@ -1607,7 +1607,7 @@
         <v>0.07206738650110425</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.02927859994366654</v>
+        <v>0.02927859986571662</v>
       </c>
     </row>
     <row r="75">
@@ -1618,7 +1618,7 @@
         <v>-0.0482064756652078</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-0.02502836508559387</v>
+        <v>-0.0250283646518741</v>
       </c>
     </row>
     <row r="76">
@@ -1629,7 +1629,7 @@
         <v>-0.06670323746131065</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>-0.04248689185744259</v>
+        <v>-0.04248689147271349</v>
       </c>
     </row>
     <row r="77">
@@ -1640,7 +1640,7 @@
         <v>-0.1676063446518038</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>-0.05917456638001409</v>
+        <v>-0.05917456649142699</v>
       </c>
     </row>
     <row r="78">
@@ -1651,7 +1651,7 @@
         <v>0.09985373784843675</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.1004174839562125</v>
+        <v>0.1004174840674992</v>
       </c>
     </row>
     <row r="79">
@@ -1662,7 +1662,7 @@
         <v>0.004247792471245068</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.0075609937143513</v>
+        <v>0.007560993390064456</v>
       </c>
     </row>
     <row r="80">
@@ -1673,7 +1673,7 @@
         <v>0.06678052775027224</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.06204307972071473</v>
+        <v>0.06204307974958587</v>
       </c>
     </row>
     <row r="81">
@@ -1684,7 +1684,7 @@
         <v>0.07069760291997175</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.0353919204283569</v>
+        <v>0.03539191987199439</v>
       </c>
     </row>
     <row r="82">
@@ -1695,7 +1695,7 @@
         <v>0.002963455062672685</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>-0.01487788983008512</v>
+        <v>-0.01487788946211403</v>
       </c>
     </row>
     <row r="83">
@@ -1706,7 +1706,7 @@
         <v>-0.01976019159151884</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.02709824906346938</v>
+        <v>-0.0270982497928306</v>
       </c>
     </row>
     <row r="84">
@@ -1717,7 +1717,7 @@
         <v>0.02076694896278813</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.02527055541667522</v>
+        <v>0.02527055547972409</v>
       </c>
     </row>
     <row r="85">
@@ -1728,7 +1728,7 @@
         <v>0.1138726461826266</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.04997765734784302</v>
+        <v>0.04997765722030623</v>
       </c>
     </row>
     <row r="86">
@@ -1739,7 +1739,7 @@
         <v>0.0863300868375526</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.02952371269523235</v>
+        <v>0.02952371267760976</v>
       </c>
     </row>
     <row r="87">
@@ -1750,7 +1750,7 @@
         <v>0.0290323743679554</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>-0.01240642631692593</v>
+        <v>-0.01240642626033056</v>
       </c>
     </row>
     <row r="88">
@@ -1761,7 +1761,7 @@
         <v>0.0323510740028403</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.01294189871842352</v>
+        <v>0.01294189887641626</v>
       </c>
     </row>
     <row r="89">
@@ -1772,7 +1772,7 @@
         <v>0.001187989845889644</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.03742807533337852</v>
+        <v>0.03742807550493847</v>
       </c>
     </row>
     <row r="90">
@@ -1783,7 +1783,7 @@
         <v>0.0235277295748508</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.0005421060586704085</v>
+        <v>0.0005421055571272707</v>
       </c>
     </row>
     <row r="91">
@@ -1794,7 +1794,7 @@
         <v>0.03436338529690337</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.007174088778612199</v>
+        <v>0.007174088572342188</v>
       </c>
     </row>
     <row r="92">
@@ -1805,7 +1805,7 @@
         <v>-0.005238501108997855</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.006665568933330828</v>
+        <v>0.006665569391887116</v>
       </c>
     </row>
     <row r="93">
@@ -1816,7 +1816,7 @@
         <v>-0.04397554540412282</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>-0.001684561263260503</v>
+        <v>-0.001684561433368849</v>
       </c>
     </row>
     <row r="94">
@@ -1827,7 +1827,7 @@
         <v>0.03903511321882387</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.02320069800647107</v>
+        <v>0.02320069799601338</v>
       </c>
     </row>
     <row r="95">
@@ -1838,7 +1838,7 @@
         <v>-0.02352828398363307</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>-0.008133471897806001</v>
+        <v>-0.00813347172338306</v>
       </c>
     </row>
     <row r="96">
@@ -1849,7 +1849,7 @@
         <v>0.008119557267448457</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.01753800014135151</v>
+        <v>0.01753800021027732</v>
       </c>
     </row>
     <row r="97">
@@ -1860,7 +1860,7 @@
         <v>-0.03487057144530385</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>-0.006138495555229107</v>
+        <v>-0.006138495822780811</v>
       </c>
     </row>
     <row r="98">
@@ -1871,7 +1871,7 @@
         <v>0.03877293711315413</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.01908879113483927</v>
+        <v>0.01908879116143317</v>
       </c>
     </row>
     <row r="99">
@@ -1882,7 +1882,7 @@
         <v>0.002924092229436752</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-0.004416279005414903</v>
+        <v>-0.0044162790328264</v>
       </c>
     </row>
     <row r="100">
@@ -1893,7 +1893,7 @@
         <v>-0.04678409171731265</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.005929697768733611</v>
+        <v>0.005929697681808897</v>
       </c>
     </row>
     <row r="101">
@@ -1904,7 +1904,7 @@
         <v>0.02160171429843119</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.002369401685986447</v>
+        <v>0.002369401647356605</v>
       </c>
     </row>
     <row r="102">
@@ -1915,7 +1915,7 @@
         <v>-0.04929689726997008</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>-0.009432437930342357</v>
+        <v>-0.009432437794156326</v>
       </c>
     </row>
     <row r="103">
@@ -1926,7 +1926,7 @@
         <v>0.009638364803493562</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-0.003265109939313502</v>
+        <v>-0.00326510997410868</v>
       </c>
     </row>
     <row r="104">
@@ -1937,7 +1937,7 @@
         <v>-0.07940058726618622</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-0.03376211190046922</v>
+        <v>-0.03376211178309475</v>
       </c>
     </row>
     <row r="105">
@@ -1948,7 +1948,7 @@
         <v>0.00225283218921265</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.007045676429648514</v>
+        <v>0.007045676376755605</v>
       </c>
     </row>
     <row r="106">
@@ -1959,7 +1959,7 @@
         <v>0.0194592200082402</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>-0.004344407335357057</v>
+        <v>-0.004344407317424614</v>
       </c>
     </row>
     <row r="107">
@@ -1970,7 +1970,7 @@
         <v>-0.1019411321476542</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>-0.04716076526397222</v>
+        <v>-0.04716076525371982</v>
       </c>
     </row>
     <row r="108">
@@ -1981,7 +1981,7 @@
         <v>0.001203819237218551</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>-0.02898275132140758</v>
+        <v>-0.02898275129818562</v>
       </c>
     </row>
     <row r="109">
@@ -1992,7 +1992,7 @@
         <v>0.13016429684924</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.13672730681815</v>
+        <v>0.1367273068063817</v>
       </c>
     </row>
     <row r="110">
@@ -2003,7 +2003,7 @@
         <v>-0.02161397376045171</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>-0.03505579169136976</v>
+        <v>-0.03505579172725707</v>
       </c>
     </row>
     <row r="111">
@@ -2014,7 +2014,7 @@
         <v>0.06590833620845173</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.0296920626657074</v>
+        <v>0.02969206256979659</v>
       </c>
     </row>
     <row r="112">
@@ -2025,7 +2025,7 @@
         <v>-0.04502747129102448</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>-0.0003239716824527559</v>
+        <v>-0.0003239717758208166</v>
       </c>
     </row>
     <row r="113">
@@ -2036,7 +2036,7 @@
         <v>0.03462702520974735</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.03433484291448198</v>
+        <v>0.03433484292635736</v>
       </c>
     </row>
     <row r="114">
@@ -2047,7 +2047,7 @@
         <v>0.006221408189294738</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.03284531927904573</v>
+        <v>0.0328453193394511</v>
       </c>
     </row>
     <row r="115">
@@ -2058,7 +2058,7 @@
         <v>-0.001498942229409791</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.0211764259967715</v>
+        <v>0.02117642596643819</v>
       </c>
     </row>
     <row r="116">
@@ -2069,7 +2069,7 @@
         <v>0.03338471222996842</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.002255221206841292</v>
+        <v>0.002255221227168348</v>
       </c>
     </row>
     <row r="117">
@@ -2080,7 +2080,7 @@
         <v>0.0403096139031283</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.02470330265404508</v>
+        <v>0.02470330263373569</v>
       </c>
     </row>
     <row r="118">
@@ -2091,7 +2091,7 @@
         <v>-0.04637740616986598</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>-0.03108599775753644</v>
+        <v>-0.03108599772549688</v>
       </c>
     </row>
     <row r="119">
@@ -2102,7 +2102,7 @@
         <v>-0.0131917396815385</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>-0.01949458909061902</v>
+        <v>-0.0194945890245552</v>
       </c>
     </row>
     <row r="120">
@@ -2113,7 +2113,7 @@
         <v>-0.03193660996460233</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>-0.02266454828625836</v>
+        <v>-0.022664548253229</v>
       </c>
     </row>
     <row r="121">
@@ -2124,7 +2124,7 @@
         <v>0.07971419850955186</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.06364275556750981</v>
+        <v>0.06364275547966883</v>
       </c>
     </row>
     <row r="122">
@@ -2135,7 +2135,7 @@
         <v>0.04703396367444367</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.03759026108932309</v>
+        <v>0.03759026104415096</v>
       </c>
     </row>
     <row r="123">
@@ -2146,7 +2146,7 @@
         <v>-0.01585787527416958</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>-0.007217413914594</v>
+        <v>-0.007217413861557577</v>
       </c>
     </row>
     <row r="124">
@@ -2157,7 +2157,7 @@
         <v>0.03022495642883836</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>-0.004342256364362072</v>
+        <v>-0.004342256575710102</v>
       </c>
     </row>
     <row r="125">
@@ -2168,7 +2168,7 @@
         <v>0.02917740961821971</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>-0.01953843358682639</v>
+        <v>-0.01953843393865837</v>
       </c>
     </row>
     <row r="126">
@@ -2179,7 +2179,7 @@
         <v>0.01123730081200413</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.01619223792464995</v>
+        <v>0.0161922377797206</v>
       </c>
     </row>
     <row r="127">
@@ -2190,7 +2190,7 @@
         <v>0.01648872644524583</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.008240642931672834</v>
+        <v>0.008240643323985029</v>
       </c>
     </row>
     <row r="128">
@@ -2201,7 +2201,7 @@
         <v>0.0007354646659207265</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>-0.01724511209072544</v>
+        <v>-0.01724511257095454</v>
       </c>
     </row>
     <row r="129">
@@ -2212,7 +2212,7 @@
         <v>0.003334579349555053</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.02113785141336661</v>
+        <v>0.02113785160145753</v>
       </c>
     </row>
     <row r="130">
@@ -2223,7 +2223,7 @@
         <v>0.01638387548657119</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.03598561707515507</v>
+        <v>0.035985617226017</v>
       </c>
     </row>
     <row r="131">
@@ -2234,7 +2234,7 @@
         <v>0.033666084053502</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.05509212861079952</v>
+        <v>0.05509212824741899</v>
       </c>
     </row>
     <row r="132">
@@ -2245,7 +2245,7 @@
         <v>-0.04458566957284057</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>-0.008899447771733012</v>
+        <v>-0.008899448039595201</v>
       </c>
     </row>
     <row r="133">
@@ -2256,7 +2256,7 @@
         <v>-0.02738335071421504</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>-0.03019807265952832</v>
+        <v>-0.03019807292186837</v>
       </c>
     </row>
     <row r="134">
@@ -2267,7 +2267,7 @@
         <v>-0.003693654035491267</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.004458709267329563</v>
+        <v>0.004458709194749865</v>
       </c>
     </row>
     <row r="135">
@@ -2278,7 +2278,7 @@
         <v>0.005809586069590342</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>-0.01012098238772375</v>
+        <v>-0.01012098237064429</v>
       </c>
     </row>
     <row r="136">
@@ -2289,7 +2289,7 @@
         <v>-0.01602392225709455</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.001975471167465166</v>
+        <v>0.001975471124104984</v>
       </c>
     </row>
     <row r="137">
@@ -2300,7 +2300,7 @@
         <v>0.02116303136744554</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.0119798227523798</v>
+        <v>0.01197982270640709</v>
       </c>
     </row>
     <row r="138">
@@ -2311,7 +2311,7 @@
         <v>0.01716310963292009</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.01107818093411083</v>
+        <v>0.01107818091885257</v>
       </c>
     </row>
     <row r="139">
@@ -2322,7 +2322,7 @@
         <v>0.04571108411379798</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.04087487678577695</v>
+        <v>0.0408748768225022</v>
       </c>
     </row>
     <row r="140">
@@ -2333,7 +2333,7 @@
         <v>0.05114499695263859</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.02695355156794078</v>
+        <v>0.02695355150691722</v>
       </c>
     </row>
     <row r="141">
@@ -2344,7 +2344,7 @@
         <v>0.01207650834328272</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.001105337523106104</v>
+        <v>0.001105337613598443</v>
       </c>
     </row>
     <row r="142">
@@ -2355,7 +2355,7 @@
         <v>0.009490382556151769</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.01548353081089248</v>
+        <v>0.01548353080167544</v>
       </c>
     </row>
     <row r="143">
@@ -2366,7 +2366,7 @@
         <v>0.05080959391353825</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.02771801353531576</v>
+        <v>0.02771801345839262</v>
       </c>
     </row>
     <row r="144">
@@ -2377,7 +2377,7 @@
         <v>0.0494642092634302</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.0307273311505363</v>
+        <v>0.03072733112833025</v>
       </c>
     </row>
     <row r="145">
@@ -2388,7 +2388,7 @@
         <v>-0.009290385971130546</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.005776013101891433</v>
+        <v>0.005776013045626965</v>
       </c>
     </row>
     <row r="146">
@@ -2399,7 +2399,7 @@
         <v>0.03121426216286869</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.01025740007933732</v>
+        <v>0.01025740003853813</v>
       </c>
     </row>
   </sheetData>
